--- a/data/trans_dic/P02E$contratada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,32</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 11,17</t>
+          <t>2,48; 10,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,88</t>
+          <t>1,08; 9,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,48</t>
+          <t>0,96; 8,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 9,47</t>
+          <t>2,3; 9,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,02</t>
+          <t>2,06; 10,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,71</t>
+          <t>1,19; 5,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,02</t>
+          <t>2,81; 8,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,6</t>
+          <t>2,38; 7,55</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 15,98</t>
+          <t>1,95; 17,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,72</t>
+          <t>0,0; 6,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,68</t>
+          <t>0,0; 7,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 5,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,15</t>
+          <t>0,45; 4,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 7,57</t>
+          <t>0,65; 6,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,17</t>
+          <t>1,23; 7,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,38</t>
+          <t>0,31; 3,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,2</t>
+          <t>1,16; 5,49</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,19</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,78</t>
+          <t>0,5; 4,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,16</t>
+          <t>0,71; 6,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,08</t>
+          <t>0,0; 8,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,5</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,04</t>
+          <t>0,48; 4,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,31</t>
+          <t>0,63; 3,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,8</t>
+          <t>0,51; 4,37</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,21</t>
+          <t>0,4; 4,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,8</t>
+          <t>1,2; 6,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,83</t>
+          <t>0,51; 3,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,62</t>
+          <t>0,29; 2,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,12</t>
+          <t>0,96; 3,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,15</t>
+          <t>0,39; 2,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,57</t>
+          <t>0,38; 2,32</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,96</t>
+          <t>0,6; 5,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,58</t>
+          <t>0,59; 3,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,25</t>
+          <t>0,51; 4,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,51</t>
+          <t>0,67; 3,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,63</t>
+          <t>0,79; 3,67</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,75</t>
+          <t>0,37; 3,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,61</t>
+          <t>0,65; 6,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,68</t>
+          <t>0,36; 3,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,37</t>
+          <t>0,53; 5,63</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,23</t>
+          <t>0,85; 3,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,8</t>
+          <t>0,97; 2,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,68</t>
+          <t>1,36; 3,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,89</t>
+          <t>1,07; 3,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,69</t>
+          <t>1,26; 2,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,07</t>
+          <t>1,33; 3,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,59</t>
+          <t>1,14; 2,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,46</t>
+          <t>1,33; 2,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,91</t>
+          <t>1,53; 2,91</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6065</t>
+          <t>0; 6000</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3687; 16843</t>
+          <t>3738; 15658</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1062; 9571</t>
+          <t>1049; 9452</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1034; 11129</t>
+          <t>1019; 9520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3082; 15498</t>
+          <t>3769; 15094</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2840; 12876</t>
+          <t>2947; 14307</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2588; 12568</t>
+          <t>2615; 12024</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7766; 25210</t>
+          <t>8835; 26590</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6011; 18222</t>
+          <t>5703; 18104</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1704; 13620</t>
+          <t>1664; 15280</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 10377</t>
+          <t>0; 9533</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>897; 8227</t>
+          <t>0; 8133</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7094</t>
+          <t>0; 7765</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>900; 8219</t>
+          <t>887; 8161</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1021; 11907</t>
+          <t>1028; 9526</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3052; 16337</t>
+          <t>2809; 17029</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1063; 11915</t>
+          <t>1094; 13316</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2271; 13748</t>
+          <t>3078; 14513</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7464</t>
+          <t>0; 5928</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>964; 9301</t>
+          <t>970; 8784</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>996; 8628</t>
+          <t>999; 9363</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4772</t>
+          <t>0; 5869</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6019</t>
+          <t>0; 5385</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>895; 7600</t>
+          <t>895; 8865</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1899; 10069</t>
+          <t>1916; 10829</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>990; 9334</t>
+          <t>1001; 8505</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 8192</t>
+          <t>0; 7498</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4693</t>
+          <t>0; 5062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1049; 10787</t>
+          <t>1035; 11357</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3483; 16949</t>
+          <t>2983; 17248</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2059; 15273</t>
+          <t>2034; 15106</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>907; 8089</t>
+          <t>901; 8020</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4488; 19917</t>
+          <t>4645; 19254</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2837; 15885</t>
+          <t>2907; 17023</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2964; 14540</t>
+          <t>2158; 13103</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2023</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7753</t>
+          <t>0; 7619</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>791; 8108</t>
+          <t>811; 8110</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1999</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2269; 12804</t>
+          <t>2100; 12383</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1037; 10600</t>
+          <t>1262; 11467</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3473; 17324</t>
+          <t>3310; 16623</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2897; 13980</t>
+          <t>3050; 14138</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1906</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1698</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2038</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7892</t>
+          <t>0; 7545</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1060; 10733</t>
+          <t>1062; 9828</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1110; 10907</t>
+          <t>1256; 12143</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 7912</t>
+          <t>0; 7226</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1156; 10859</t>
+          <t>1054; 10265</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1280; 11483</t>
+          <t>1135; 12033</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5288; 20210</t>
+          <t>5347; 19648</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9777; 27556</t>
+          <t>9537; 27679</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11013; 27773</t>
+          <t>10304; 27496</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10302; 29074</t>
+          <t>10713; 30638</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>18356; 40758</t>
+          <t>19038; 41519</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14921; 34030</t>
+          <t>14683; 34989</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19712; 42312</t>
+          <t>18606; 41998</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>32529; 61428</t>
+          <t>33221; 60973</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28141; 54303</t>
+          <t>28577; 54153</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$contratada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 10,38</t>
+          <t>2,45; 10,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,76</t>
+          <t>1,06; 9,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,97</t>
+          <t>0,95; 9,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 9,22</t>
+          <t>1,84; 9,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 10,02</t>
+          <t>1,96; 8,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,46</t>
+          <t>0,92; 5,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,45</t>
+          <t>2,72; 8,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,55</t>
+          <t>2,4; 7,95</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 17,93</t>
+          <t>1,94; 15,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,17</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,59</t>
+          <t>0,82; 7,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,44</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,12</t>
+          <t>0,46; 4,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,05</t>
+          <t>0,66; 6,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,47</t>
+          <t>1,45; 7,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,78</t>
+          <t>0,49; 3,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,49</t>
+          <t>0,85; 5,24</t>
         </is>
       </c>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,52</t>
+          <t>0,49; 4,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,69</t>
+          <t>0,71; 6,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,71</t>
+          <t>0,0; 8,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 4,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,71</t>
+          <t>0,47; 4,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,56</t>
+          <t>0,63; 3,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,37</t>
+          <t>0,52; 4,41</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,43</t>
+          <t>0,41; 4,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,92</t>
+          <t>1,24; 6,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,79</t>
+          <t>0,52; 4,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,59</t>
+          <t>0,29; 2,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,99</t>
+          <t>0,93; 3,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,3</t>
+          <t>0,38; 2,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,32</t>
+          <t>0,48; 2,61</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,96</t>
+          <t>0,59; 5,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,46</t>
+          <t>0,56; 3,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,6</t>
+          <t>0,4; 4,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,19 +1153,19 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,37</t>
+          <t>0,67; 3,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,67</t>
+          <t>0,78; 3,7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,43</t>
+          <t>0,37; 3,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,25</t>
+          <t>0,68; 6,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,48</t>
+          <t>0,36; 3,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,63</t>
+          <t>0,6; 5,42</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,14</t>
+          <t>0,92; 3,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,81</t>
+          <t>0,99; 2,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,64</t>
+          <t>1,43; 3,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,05</t>
+          <t>1,05; 2,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,74</t>
+          <t>1,21; 2,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,16</t>
+          <t>1,3; 3,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,58</t>
+          <t>1,19; 2,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,44</t>
+          <t>1,33; 2,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,91</t>
+          <t>1,52; 2,93</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6000</t>
+          <t>0; 5995</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3738; 15658</t>
+          <t>3694; 15966</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1049; 9452</t>
+          <t>1023; 9423</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1019; 9520</t>
+          <t>1005; 9811</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3769; 15094</t>
+          <t>3015; 15443</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2947; 14307</t>
+          <t>2803; 12724</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2615; 12024</t>
+          <t>2021; 11319</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8835; 26590</t>
+          <t>8569; 25951</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5703; 18104</t>
+          <t>5763; 19047</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1664; 15280</t>
+          <t>1656; 13013</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 9533</t>
+          <t>0; 10226</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8133</t>
+          <t>881; 8515</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7765</t>
+          <t>0; 6976</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>887; 8161</t>
+          <t>901; 8091</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1028; 9526</t>
+          <t>1040; 10350</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2809; 17029</t>
+          <t>3316; 16862</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1094; 13316</t>
+          <t>1730; 13366</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3078; 14513</t>
+          <t>2247; 13873</t>
         </is>
       </c>
     </row>
@@ -1965,27 +1965,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5928</t>
+          <t>0; 6618</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>970; 8784</t>
+          <t>960; 9364</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>999; 9363</t>
+          <t>1001; 8752</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5869</t>
+          <t>0; 5748</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5385</t>
+          <t>0; 5187</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>895; 8865</t>
+          <t>883; 8452</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1916; 10829</t>
+          <t>1920; 10663</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1001; 8505</t>
+          <t>1005; 8583</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7498</t>
+          <t>0; 7357</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5062</t>
+          <t>0; 5616</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1035; 11357</t>
+          <t>1046; 11203</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2983; 17248</t>
+          <t>3104; 16494</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2034; 15106</t>
+          <t>2066; 16072</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>901; 8020</t>
+          <t>910; 8633</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4645; 19254</t>
+          <t>4485; 19273</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2907; 17023</t>
+          <t>2837; 16280</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2158; 13103</t>
+          <t>2701; 14747</t>
         </is>
       </c>
     </row>
@@ -2296,12 +2296,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7619</t>
+          <t>0; 7751</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>811; 8110</t>
+          <t>797; 7980</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2100; 12383</t>
+          <t>2003; 13011</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1262; 11467</t>
+          <t>986; 11237</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2326,19 +2326,19 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3310; 16623</t>
+          <t>3300; 15350</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3050; 14138</t>
+          <t>2995; 14265</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7545</t>
+          <t>0; 7655</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1062; 9828</t>
+          <t>1066; 9903</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1256; 12143</t>
+          <t>1323; 11683</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 7226</t>
+          <t>0; 7570</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1054; 10265</t>
+          <t>1051; 9676</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1135; 12033</t>
+          <t>1273; 11584</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5347; 19648</t>
+          <t>5776; 21178</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9537; 27679</t>
+          <t>9748; 28174</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10304; 27496</t>
+          <t>10780; 27727</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10713; 30638</t>
+          <t>10567; 29494</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19038; 41519</t>
+          <t>18271; 41916</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14683; 34989</t>
+          <t>14400; 34945</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18606; 41998</t>
+          <t>19466; 42967</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>33221; 60973</t>
+          <t>33141; 63069</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28577; 54153</t>
+          <t>28251; 54628</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$contratada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
